--- a/Team-Data/2008-09/1-12-2008-09.xlsx
+++ b/Team-Data/2008-09/1-12-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,28 +806,28 @@
         <v>1.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AF2" t="n">
         <v>10</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AG2" t="n">
         <v>11</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>12</v>
       </c>
       <c r="AH2" t="n">
         <v>22</v>
       </c>
       <c r="AI2" t="n">
+        <v>22</v>
+      </c>
+      <c r="AJ2" t="n">
         <v>23</v>
       </c>
-      <c r="AJ2" t="n">
-        <v>24</v>
-      </c>
       <c r="AK2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL2" t="n">
         <v>4</v>
@@ -769,13 +836,13 @@
         <v>3</v>
       </c>
       <c r="AN2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AO2" t="n">
         <v>23</v>
       </c>
       <c r="AP2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ2" t="n">
         <v>28</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-12-2008-09</t>
+          <t>2009-01-12</t>
         </is>
       </c>
     </row>
@@ -855,67 +922,67 @@
         <v>0.769</v>
       </c>
       <c r="H3" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I3" t="n">
-        <v>36.5</v>
+        <v>36.3</v>
       </c>
       <c r="J3" t="n">
-        <v>76.5</v>
+        <v>76.2</v>
       </c>
       <c r="K3" t="n">
         <v>0.477</v>
       </c>
       <c r="L3" t="n">
-        <v>6.3</v>
+        <v>6.1</v>
       </c>
       <c r="M3" t="n">
-        <v>16.9</v>
+        <v>16.7</v>
       </c>
       <c r="N3" t="n">
-        <v>0.371</v>
+        <v>0.366</v>
       </c>
       <c r="O3" t="n">
         <v>21.2</v>
       </c>
       <c r="P3" t="n">
-        <v>27.5</v>
+        <v>27.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.772</v>
+        <v>0.766</v>
       </c>
       <c r="R3" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="S3" t="n">
-        <v>32.1</v>
+        <v>31.9</v>
       </c>
       <c r="T3" t="n">
-        <v>43.1</v>
+        <v>42.8</v>
       </c>
       <c r="U3" t="n">
-        <v>22.2</v>
+        <v>21.9</v>
       </c>
       <c r="V3" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="W3" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="X3" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y3" t="n">
         <v>4.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>23.7</v>
+        <v>23.8</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.6</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AC3" t="n">
         <v>8.5</v>
@@ -933,10 +1000,10 @@
         <v>4</v>
       </c>
       <c r="AH3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AI3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AJ3" t="n">
         <v>29</v>
@@ -945,22 +1012,22 @@
         <v>3</v>
       </c>
       <c r="AL3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM3" t="n">
         <v>18</v>
       </c>
       <c r="AN3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AP3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR3" t="n">
         <v>15</v>
@@ -969,10 +1036,10 @@
         <v>6</v>
       </c>
       <c r="AT3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU3" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AV3" t="n">
         <v>29</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-12-2008-09</t>
+          <t>2009-01-12</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-3</v>
       </c>
       <c r="AD4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE4" t="n">
         <v>21</v>
@@ -1115,7 +1182,7 @@
         <v>22</v>
       </c>
       <c r="AH4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI4" t="n">
         <v>30</v>
@@ -1133,7 +1200,7 @@
         <v>25</v>
       </c>
       <c r="AN4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO4" t="n">
         <v>17</v>
@@ -1157,10 +1224,10 @@
         <v>23</v>
       </c>
       <c r="AV4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX4" t="n">
         <v>21</v>
@@ -1172,7 +1239,7 @@
         <v>21</v>
       </c>
       <c r="BA4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-12-2008-09</t>
+          <t>2009-01-12</t>
         </is>
       </c>
     </row>
@@ -1210,43 +1277,43 @@
         <v>37</v>
       </c>
       <c r="E5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G5" t="n">
-        <v>0.405</v>
+        <v>0.432</v>
       </c>
       <c r="H5" t="n">
         <v>48.5</v>
       </c>
       <c r="I5" t="n">
-        <v>37</v>
+        <v>37.1</v>
       </c>
       <c r="J5" t="n">
-        <v>84.2</v>
+        <v>84</v>
       </c>
       <c r="K5" t="n">
-        <v>0.44</v>
+        <v>0.441</v>
       </c>
       <c r="L5" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="M5" t="n">
         <v>16.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0.378</v>
+        <v>0.384</v>
       </c>
       <c r="O5" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="P5" t="n">
-        <v>23.5</v>
+        <v>23.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.801</v>
+        <v>0.798</v>
       </c>
       <c r="R5" t="n">
         <v>11.6</v>
@@ -1258,10 +1325,10 @@
         <v>41.7</v>
       </c>
       <c r="U5" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="V5" t="n">
-        <v>14.9</v>
+        <v>15.1</v>
       </c>
       <c r="W5" t="n">
         <v>7.5</v>
@@ -1270,73 +1337,73 @@
         <v>5.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>99.09999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>-4</v>
+        <v>-3.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AE5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG5" t="n">
         <v>19</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>20</v>
       </c>
       <c r="AH5" t="n">
         <v>6</v>
       </c>
       <c r="AI5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ5" t="n">
         <v>4</v>
       </c>
       <c r="AK5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AM5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP5" t="n">
         <v>20</v>
       </c>
-      <c r="AN5" t="n">
-        <v>9</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>16</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>21</v>
-      </c>
       <c r="AQ5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT5" t="n">
         <v>15</v>
       </c>
       <c r="AU5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV5" t="n">
         <v>19</v>
@@ -1351,16 +1418,16 @@
         <v>27</v>
       </c>
       <c r="AZ5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA5" t="n">
         <v>23</v>
       </c>
       <c r="BB5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BC5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-12-2008-09</t>
+          <t>2009-01-12</t>
         </is>
       </c>
     </row>
@@ -1389,94 +1456,94 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E6" t="n">
         <v>29</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>0.853</v>
+        <v>0.829</v>
       </c>
       <c r="H6" t="n">
         <v>48</v>
       </c>
       <c r="I6" t="n">
-        <v>37.7</v>
+        <v>37.5</v>
       </c>
       <c r="J6" t="n">
-        <v>78.40000000000001</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.481</v>
+        <v>0.48</v>
       </c>
       <c r="L6" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M6" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0.353</v>
+        <v>0.35</v>
       </c>
       <c r="O6" t="n">
-        <v>19.2</v>
+        <v>19.4</v>
       </c>
       <c r="P6" t="n">
-        <v>25.2</v>
+        <v>25.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.764</v>
+        <v>0.763</v>
       </c>
       <c r="R6" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S6" t="n">
-        <v>30.7</v>
+        <v>30.8</v>
       </c>
       <c r="T6" t="n">
         <v>41.6</v>
       </c>
       <c r="U6" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V6" t="n">
-        <v>13.1</v>
+        <v>13.3</v>
       </c>
       <c r="W6" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="X6" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>101.9</v>
+        <v>101.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>12.9</v>
+        <v>12.4</v>
       </c>
       <c r="AD6" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AE6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF6" t="n">
         <v>1</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH6" t="n">
         <v>28</v>
@@ -1485,7 +1552,7 @@
         <v>7</v>
       </c>
       <c r="AJ6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK6" t="n">
         <v>2</v>
@@ -1497,7 +1564,7 @@
         <v>7</v>
       </c>
       <c r="AN6" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AO6" t="n">
         <v>11</v>
@@ -1506,7 +1573,7 @@
         <v>10</v>
       </c>
       <c r="AQ6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR6" t="n">
         <v>17</v>
@@ -1521,7 +1588,7 @@
         <v>14</v>
       </c>
       <c r="AV6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW6" t="n">
         <v>5</v>
@@ -1530,13 +1597,13 @@
         <v>3</v>
       </c>
       <c r="AY6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BA6" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BB6" t="n">
         <v>8</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-12-2008-09</t>
+          <t>2009-01-12</t>
         </is>
       </c>
     </row>
@@ -1649,25 +1716,25 @@
         <v>1.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AE7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF7" t="n">
         <v>12</v>
       </c>
       <c r="AG7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI7" t="n">
         <v>6</v>
       </c>
       <c r="AJ7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK7" t="n">
         <v>17</v>
@@ -1676,7 +1743,7 @@
         <v>12</v>
       </c>
       <c r="AM7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN7" t="n">
         <v>25</v>
@@ -1688,13 +1755,13 @@
         <v>29</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR7" t="n">
         <v>9</v>
       </c>
       <c r="AS7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT7" t="n">
         <v>2</v>
@@ -1703,7 +1770,7 @@
         <v>9</v>
       </c>
       <c r="AV7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW7" t="n">
         <v>18</v>
@@ -1721,7 +1788,7 @@
         <v>27</v>
       </c>
       <c r="BB7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BC7" t="n">
         <v>12</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-12-2008-09</t>
+          <t>2009-01-12</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>3.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1840,10 +1907,10 @@
         <v>7</v>
       </c>
       <c r="AG8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI8" t="n">
         <v>11</v>
@@ -1876,7 +1943,7 @@
         <v>25</v>
       </c>
       <c r="AS8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AT8" t="n">
         <v>21</v>
@@ -1885,7 +1952,7 @@
         <v>4</v>
       </c>
       <c r="AV8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW8" t="n">
         <v>3</v>
@@ -1897,10 +1964,10 @@
         <v>25</v>
       </c>
       <c r="AZ8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB8" t="n">
         <v>5</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-12-2008-09</t>
+          <t>2009-01-12</t>
         </is>
       </c>
     </row>
@@ -2016,19 +2083,19 @@
         <v>26</v>
       </c>
       <c r="AE9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF9" t="n">
         <v>7</v>
       </c>
       <c r="AG9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AI9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ9" t="n">
         <v>20</v>
@@ -2049,7 +2116,7 @@
         <v>24</v>
       </c>
       <c r="AP9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ9" t="n">
         <v>23</v>
@@ -2058,22 +2125,22 @@
         <v>18</v>
       </c>
       <c r="AS9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT9" t="n">
         <v>19</v>
       </c>
       <c r="AU9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV9" t="n">
         <v>2</v>
       </c>
       <c r="AW9" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY9" t="n">
         <v>5</v>
@@ -2082,13 +2149,13 @@
         <v>19</v>
       </c>
       <c r="BA9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BB9" t="n">
         <v>26</v>
       </c>
       <c r="BC9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-12-2008-09</t>
+          <t>2009-01-12</t>
         </is>
       </c>
     </row>
@@ -2207,7 +2274,7 @@
         <v>26</v>
       </c>
       <c r="AH10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI10" t="n">
         <v>3</v>
@@ -2219,13 +2286,13 @@
         <v>18</v>
       </c>
       <c r="AL10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AN10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO10" t="n">
         <v>2</v>
@@ -2234,7 +2301,7 @@
         <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR10" t="n">
         <v>3</v>
@@ -2249,7 +2316,7 @@
         <v>18</v>
       </c>
       <c r="AV10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW10" t="n">
         <v>6</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-12-2008-09</t>
+          <t>2009-01-12</t>
         </is>
       </c>
     </row>
@@ -2386,10 +2453,10 @@
         <v>12</v>
       </c>
       <c r="AG11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI11" t="n">
         <v>29</v>
@@ -2401,7 +2468,7 @@
         <v>27</v>
       </c>
       <c r="AL11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM11" t="n">
         <v>10</v>
@@ -2416,16 +2483,16 @@
         <v>15</v>
       </c>
       <c r="AQ11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AR11" t="n">
         <v>21</v>
       </c>
       <c r="AS11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT11" t="n">
         <v>4</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>5</v>
       </c>
       <c r="AU11" t="n">
         <v>25</v>
@@ -2446,7 +2513,7 @@
         <v>3</v>
       </c>
       <c r="BA11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB11" t="n">
         <v>21</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-12-2008-09</t>
+          <t>2009-01-12</t>
         </is>
       </c>
     </row>
@@ -2481,97 +2548,97 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E12" t="n">
         <v>13</v>
       </c>
       <c r="F12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G12" t="n">
-        <v>0.342</v>
+        <v>0.351</v>
       </c>
       <c r="H12" t="n">
         <v>48.7</v>
       </c>
       <c r="I12" t="n">
-        <v>39.4</v>
+        <v>39.3</v>
       </c>
       <c r="J12" t="n">
-        <v>86.5</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L12" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="M12" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="N12" t="n">
-        <v>0.363</v>
+        <v>0.356</v>
       </c>
       <c r="O12" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="P12" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="R12" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="S12" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="T12" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="U12" t="n">
         <v>22.9</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0.806</v>
-      </c>
-      <c r="R12" t="n">
-        <v>11.7</v>
-      </c>
-      <c r="S12" t="n">
-        <v>32.3</v>
-      </c>
-      <c r="T12" t="n">
-        <v>44</v>
-      </c>
-      <c r="U12" t="n">
-        <v>23.2</v>
-      </c>
       <c r="V12" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="W12" t="n">
         <v>7.2</v>
       </c>
       <c r="X12" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y12" t="n">
         <v>5.7</v>
       </c>
       <c r="Z12" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="AA12" t="n">
         <v>21</v>
       </c>
       <c r="AB12" t="n">
-        <v>104.6</v>
+        <v>104.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>-2.5</v>
+        <v>-2.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AG12" t="n">
         <v>23</v>
       </c>
       <c r="AH12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI12" t="n">
         <v>2</v>
@@ -2583,7 +2650,7 @@
         <v>14</v>
       </c>
       <c r="AL12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM12" t="n">
         <v>8</v>
@@ -2592,7 +2659,7 @@
         <v>15</v>
       </c>
       <c r="AO12" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AP12" t="n">
         <v>25</v>
@@ -2601,7 +2668,7 @@
         <v>5</v>
       </c>
       <c r="AR12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AS12" t="n">
         <v>3</v>
@@ -2613,13 +2680,13 @@
         <v>3</v>
       </c>
       <c r="AV12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW12" t="n">
         <v>15</v>
       </c>
       <c r="AX12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY12" t="n">
         <v>26</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-12-2008-09</t>
+          <t>2009-01-12</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-7.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AE13" t="n">
         <v>28</v>
@@ -2774,7 +2841,7 @@
         <v>28</v>
       </c>
       <c r="AO13" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP13" t="n">
         <v>22</v>
@@ -2795,10 +2862,10 @@
         <v>27</v>
       </c>
       <c r="AV13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX13" t="n">
         <v>2</v>
@@ -2813,7 +2880,7 @@
         <v>26</v>
       </c>
       <c r="BB13" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC13" t="n">
         <v>28</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-12-2008-09</t>
+          <t>2009-01-12</t>
         </is>
       </c>
     </row>
@@ -2845,25 +2912,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F14" t="n">
         <v>6</v>
       </c>
       <c r="G14" t="n">
-        <v>0.829</v>
+        <v>0.833</v>
       </c>
       <c r="H14" t="n">
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>39.6</v>
+        <v>39.5</v>
       </c>
       <c r="J14" t="n">
-        <v>83.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K14" t="n">
         <v>0.473</v>
@@ -2872,31 +2939,31 @@
         <v>7</v>
       </c>
       <c r="M14" t="n">
-        <v>18.7</v>
+        <v>18.4</v>
       </c>
       <c r="N14" t="n">
-        <v>0.374</v>
+        <v>0.379</v>
       </c>
       <c r="O14" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="P14" t="n">
-        <v>28.5</v>
+        <v>28.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.771</v>
+        <v>0.772</v>
       </c>
       <c r="R14" t="n">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="S14" t="n">
-        <v>32.2</v>
+        <v>32.4</v>
       </c>
       <c r="T14" t="n">
-        <v>44.6</v>
+        <v>44.7</v>
       </c>
       <c r="U14" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="V14" t="n">
         <v>14.1</v>
@@ -2911,28 +2978,28 @@
         <v>4.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="AB14" t="n">
-        <v>108.1</v>
+        <v>107.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
       <c r="AD14" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="AE14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH14" t="n">
         <v>28</v>
@@ -2941,7 +3008,7 @@
         <v>1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK14" t="n">
         <v>6</v>
@@ -2950,7 +3017,7 @@
         <v>11</v>
       </c>
       <c r="AM14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AN14" t="n">
         <v>11</v>
@@ -2962,13 +3029,13 @@
         <v>3</v>
       </c>
       <c r="AQ14" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AR14" t="n">
         <v>5</v>
       </c>
       <c r="AS14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
@@ -2983,16 +3050,16 @@
         <v>2</v>
       </c>
       <c r="AX14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB14" t="n">
         <v>1</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-12-2008-09</t>
+          <t>2009-01-12</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-5.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AE15" t="n">
         <v>24</v>
@@ -3138,7 +3205,7 @@
         <v>27</v>
       </c>
       <c r="AO15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP15" t="n">
         <v>12</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-12-2008-09</t>
+          <t>2009-01-12</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-0.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE16" t="n">
         <v>15</v>
@@ -3299,7 +3366,7 @@
         <v>15</v>
       </c>
       <c r="AH16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI16" t="n">
         <v>16</v>
@@ -3317,7 +3384,7 @@
         <v>11</v>
       </c>
       <c r="AN16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO16" t="n">
         <v>27</v>
@@ -3341,7 +3408,7 @@
         <v>26</v>
       </c>
       <c r="AV16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW16" t="n">
         <v>7</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-12-2008-09</t>
+          <t>2009-01-12</t>
         </is>
       </c>
     </row>
@@ -3394,22 +3461,22 @@
         <v>39</v>
       </c>
       <c r="E17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G17" t="n">
-        <v>0.487</v>
+        <v>0.462</v>
       </c>
       <c r="H17" t="n">
         <v>48.4</v>
       </c>
       <c r="I17" t="n">
-        <v>36.3</v>
+        <v>36.2</v>
       </c>
       <c r="J17" t="n">
-        <v>81.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K17" t="n">
         <v>0.445</v>
@@ -3418,46 +3485,46 @@
         <v>5.3</v>
       </c>
       <c r="M17" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="N17" t="n">
-        <v>0.342</v>
+        <v>0.346</v>
       </c>
       <c r="O17" t="n">
         <v>19.6</v>
       </c>
       <c r="P17" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.781</v>
+        <v>0.778</v>
       </c>
       <c r="R17" t="n">
         <v>12.4</v>
       </c>
       <c r="S17" t="n">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="T17" t="n">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="U17" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="V17" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W17" t="n">
         <v>6.9</v>
       </c>
       <c r="X17" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Y17" t="n">
         <v>4.8</v>
       </c>
       <c r="Z17" t="n">
-        <v>23.9</v>
+        <v>24.2</v>
       </c>
       <c r="AA17" t="n">
         <v>22.9</v>
@@ -3466,28 +3533,28 @@
         <v>97.40000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AD17" t="n">
         <v>1</v>
       </c>
       <c r="AE17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG17" t="n">
         <v>17</v>
       </c>
       <c r="AH17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI17" t="n">
         <v>17</v>
       </c>
       <c r="AJ17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK17" t="n">
         <v>22</v>
@@ -3499,7 +3566,7 @@
         <v>24</v>
       </c>
       <c r="AN17" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AO17" t="n">
         <v>9</v>
@@ -3514,7 +3581,7 @@
         <v>3</v>
       </c>
       <c r="AS17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT17" t="n">
         <v>8</v>
@@ -3523,7 +3590,7 @@
         <v>12</v>
       </c>
       <c r="AV17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW17" t="n">
         <v>22</v>
@@ -3544,7 +3611,7 @@
         <v>17</v>
       </c>
       <c r="BC17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-12-2008-09</t>
+          <t>2009-01-12</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3718,13 @@
         <v>-4.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE18" t="n">
         <v>24</v>
       </c>
       <c r="AF18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG18" t="n">
         <v>24</v>
@@ -3681,7 +3748,7 @@
         <v>23</v>
       </c>
       <c r="AN18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO18" t="n">
         <v>10</v>
@@ -3693,7 +3760,7 @@
         <v>17</v>
       </c>
       <c r="AR18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS18" t="n">
         <v>22</v>
@@ -3708,7 +3775,7 @@
         <v>15</v>
       </c>
       <c r="AW18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AX18" t="n">
         <v>23</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-12-2008-09</t>
+          <t>2009-01-12</t>
         </is>
       </c>
     </row>
@@ -3755,55 +3822,55 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F19" t="n">
         <v>19</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5</v>
+        <v>0.486</v>
       </c>
       <c r="H19" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
       <c r="I19" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="J19" t="n">
-        <v>81</v>
+        <v>80.5</v>
       </c>
       <c r="K19" t="n">
-        <v>0.441</v>
+        <v>0.442</v>
       </c>
       <c r="L19" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="M19" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="N19" t="n">
-        <v>0.374</v>
+        <v>0.379</v>
       </c>
       <c r="O19" t="n">
         <v>20.3</v>
       </c>
       <c r="P19" t="n">
-        <v>25.9</v>
+        <v>26</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.784</v>
+        <v>0.783</v>
       </c>
       <c r="R19" t="n">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
       <c r="S19" t="n">
         <v>30</v>
       </c>
       <c r="T19" t="n">
-        <v>41.5</v>
+        <v>41.3</v>
       </c>
       <c r="U19" t="n">
         <v>19.4</v>
@@ -3812,10 +3879,10 @@
         <v>13.7</v>
       </c>
       <c r="W19" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="X19" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y19" t="n">
         <v>5.4</v>
@@ -3827,16 +3894,16 @@
         <v>21.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>99.5</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>-1.8</v>
+        <v>-1.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF19" t="n">
         <v>16</v>
@@ -3848,7 +3915,7 @@
         <v>3</v>
       </c>
       <c r="AI19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ19" t="n">
         <v>14</v>
@@ -3860,13 +3927,13 @@
         <v>5</v>
       </c>
       <c r="AM19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN19" t="n">
         <v>10</v>
       </c>
       <c r="AO19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP19" t="n">
         <v>8</v>
@@ -3878,7 +3945,7 @@
         <v>14</v>
       </c>
       <c r="AS19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT19" t="n">
         <v>17</v>
@@ -3890,7 +3957,7 @@
         <v>11</v>
       </c>
       <c r="AW19" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX19" t="n">
         <v>19</v>
@@ -3902,7 +3969,7 @@
         <v>27</v>
       </c>
       <c r="BA19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB19" t="n">
         <v>11</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-12-2008-09</t>
+          <t>2009-01-12</t>
         </is>
       </c>
     </row>
@@ -3937,94 +4004,94 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E20" t="n">
         <v>22</v>
       </c>
       <c r="F20" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G20" t="n">
-        <v>0.647</v>
+        <v>0.667</v>
       </c>
       <c r="H20" t="n">
         <v>48</v>
       </c>
       <c r="I20" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="J20" t="n">
-        <v>76.59999999999999</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.457</v>
+        <v>0.459</v>
       </c>
       <c r="L20" t="n">
         <v>7.6</v>
       </c>
       <c r="M20" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0.391</v>
+        <v>0.394</v>
       </c>
       <c r="O20" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="P20" t="n">
         <v>22.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.806</v>
       </c>
       <c r="R20" t="n">
-        <v>9.699999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="S20" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="T20" t="n">
-        <v>39.1</v>
+        <v>38.7</v>
       </c>
       <c r="U20" t="n">
         <v>19.9</v>
       </c>
       <c r="V20" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="W20" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="X20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y20" t="n">
         <v>3.6</v>
       </c>
       <c r="Z20" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AB20" t="n">
         <v>96</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AE20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AF20" t="n">
         <v>5</v>
       </c>
       <c r="AG20" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AH20" t="n">
         <v>30</v>
@@ -4036,7 +4103,7 @@
         <v>28</v>
       </c>
       <c r="AK20" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AL20" t="n">
         <v>7</v>
@@ -4045,19 +4112,19 @@
         <v>12</v>
       </c>
       <c r="AN20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP20" t="n">
         <v>26</v>
       </c>
       <c r="AQ20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AR20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS20" t="n">
         <v>25</v>
@@ -4069,13 +4136,13 @@
         <v>24</v>
       </c>
       <c r="AV20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW20" t="n">
         <v>8</v>
       </c>
       <c r="AX20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY20" t="n">
         <v>3</v>
@@ -4084,13 +4151,13 @@
         <v>15</v>
       </c>
       <c r="BA20" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BB20" t="n">
         <v>23</v>
       </c>
       <c r="BC20" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-12-2008-09</t>
+          <t>2009-01-12</t>
         </is>
       </c>
     </row>
@@ -4119,37 +4186,37 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F21" t="n">
         <v>22</v>
       </c>
       <c r="G21" t="n">
-        <v>0.389</v>
+        <v>0.371</v>
       </c>
       <c r="H21" t="n">
         <v>48.1</v>
       </c>
       <c r="I21" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J21" t="n">
-        <v>86.7</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="K21" t="n">
         <v>0.432</v>
       </c>
       <c r="L21" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="M21" t="n">
-        <v>29.2</v>
+        <v>29.3</v>
       </c>
       <c r="N21" t="n">
-        <v>0.353</v>
+        <v>0.354</v>
       </c>
       <c r="O21" t="n">
         <v>17.6</v>
@@ -4158,10 +4225,10 @@
         <v>22</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.797</v>
+        <v>0.8</v>
       </c>
       <c r="R21" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S21" t="n">
         <v>31.6</v>
@@ -4170,46 +4237,46 @@
         <v>42.5</v>
       </c>
       <c r="U21" t="n">
-        <v>21.5</v>
+        <v>21.3</v>
       </c>
       <c r="V21" t="n">
-        <v>15.3</v>
+        <v>15.5</v>
       </c>
       <c r="W21" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X21" t="n">
         <v>2.3</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AA21" t="n">
         <v>18.6</v>
       </c>
       <c r="AB21" t="n">
-        <v>102.8</v>
+        <v>102.9</v>
       </c>
       <c r="AC21" t="n">
-        <v>-3.5</v>
+        <v>-3.8</v>
       </c>
       <c r="AD21" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AF21" t="n">
         <v>20</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>19</v>
       </c>
       <c r="AG21" t="n">
         <v>21</v>
       </c>
       <c r="AH21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI21" t="n">
         <v>8</v>
@@ -4227,16 +4294,16 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP21" t="n">
         <v>28</v>
       </c>
       <c r="AQ21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AR21" t="n">
         <v>16</v>
@@ -4248,10 +4315,10 @@
         <v>9</v>
       </c>
       <c r="AU21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AV21" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AW21" t="n">
         <v>13</v>
@@ -4272,7 +4339,7 @@
         <v>6</v>
       </c>
       <c r="BC21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-12-2008-09</t>
+          <t>2009-01-12</t>
         </is>
       </c>
     </row>
@@ -4301,19 +4368,19 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E22" t="n">
         <v>6</v>
       </c>
       <c r="F22" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G22" t="n">
-        <v>0.154</v>
+        <v>0.158</v>
       </c>
       <c r="H22" t="n">
-        <v>48.3</v>
+        <v>48.1</v>
       </c>
       <c r="I22" t="n">
         <v>36.4</v>
@@ -4322,7 +4389,7 @@
         <v>82</v>
       </c>
       <c r="K22" t="n">
-        <v>0.443</v>
+        <v>0.444</v>
       </c>
       <c r="L22" t="n">
         <v>3.9</v>
@@ -4331,55 +4398,55 @@
         <v>10.6</v>
       </c>
       <c r="N22" t="n">
-        <v>0.365</v>
+        <v>0.366</v>
       </c>
       <c r="O22" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="P22" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.759</v>
+        <v>0.757</v>
       </c>
       <c r="R22" t="n">
         <v>11.7</v>
       </c>
       <c r="S22" t="n">
-        <v>30.6</v>
+        <v>30.4</v>
       </c>
       <c r="T22" t="n">
-        <v>42.3</v>
+        <v>42.1</v>
       </c>
       <c r="U22" t="n">
         <v>20.1</v>
       </c>
       <c r="V22" t="n">
-        <v>16.5</v>
+        <v>16.3</v>
       </c>
       <c r="W22" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X22" t="n">
         <v>4.7</v>
       </c>
       <c r="Y22" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Z22" t="n">
         <v>21</v>
       </c>
       <c r="AA22" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AB22" t="n">
-        <v>95.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="AC22" t="n">
-        <v>-8.1</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE22" t="n">
         <v>30</v>
@@ -4391,10 +4458,10 @@
         <v>30</v>
       </c>
       <c r="AH22" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AI22" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AJ22" t="n">
         <v>9</v>
@@ -4409,25 +4476,25 @@
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO22" t="n">
         <v>20</v>
       </c>
       <c r="AP22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS22" t="n">
         <v>12</v>
       </c>
-      <c r="AS22" t="n">
+      <c r="AT22" t="n">
         <v>11</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>10</v>
       </c>
       <c r="AU22" t="n">
         <v>21</v>
@@ -4436,7 +4503,7 @@
         <v>30</v>
       </c>
       <c r="AW22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX22" t="n">
         <v>20</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-12-2008-09</t>
+          <t>2009-01-12</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>7.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4573,7 +4640,7 @@
         <v>3</v>
       </c>
       <c r="AH23" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI23" t="n">
         <v>20</v>
@@ -4591,7 +4658,7 @@
         <v>2</v>
       </c>
       <c r="AN23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO23" t="n">
         <v>13</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-12-2008-09</t>
+          <t>2009-01-12</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-0.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AE24" t="n">
         <v>18</v>
@@ -4776,7 +4843,7 @@
         <v>29</v>
       </c>
       <c r="AO24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP24" t="n">
         <v>13</v>
@@ -4803,13 +4870,13 @@
         <v>10</v>
       </c>
       <c r="AX24" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY24" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA24" t="n">
         <v>21</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-12-2008-09</t>
+          <t>2009-01-12</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>2</v>
       </c>
       <c r="AD25" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE25" t="n">
         <v>14</v>
@@ -4934,10 +5001,10 @@
         <v>7</v>
       </c>
       <c r="AG25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI25" t="n">
         <v>4</v>
@@ -4958,7 +5025,7 @@
         <v>2</v>
       </c>
       <c r="AO25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP25" t="n">
         <v>6</v>
@@ -4976,7 +5043,7 @@
         <v>18</v>
       </c>
       <c r="AU25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV25" t="n">
         <v>28</v>
@@ -4988,7 +5055,7 @@
         <v>18</v>
       </c>
       <c r="AY25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ25" t="n">
         <v>8</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-12-2008-09</t>
+          <t>2009-01-12</t>
         </is>
       </c>
     </row>
@@ -5032,94 +5099,94 @@
         <v>36</v>
       </c>
       <c r="E26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G26" t="n">
-        <v>0.639</v>
+        <v>0.611</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="J26" t="n">
-        <v>78.7</v>
+        <v>79</v>
       </c>
       <c r="K26" t="n">
-        <v>0.46</v>
+        <v>0.457</v>
       </c>
       <c r="L26" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="M26" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="N26" t="n">
-        <v>0.387</v>
+        <v>0.385</v>
       </c>
       <c r="O26" t="n">
-        <v>18.7</v>
+        <v>18.1</v>
       </c>
       <c r="P26" t="n">
-        <v>24</v>
+        <v>23.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.778</v>
+        <v>0.77</v>
       </c>
       <c r="R26" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="S26" t="n">
         <v>27.4</v>
       </c>
       <c r="T26" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="U26" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="V26" t="n">
         <v>12.8</v>
       </c>
       <c r="W26" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X26" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="Z26" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="AA26" t="n">
         <v>20.9</v>
       </c>
-      <c r="AA26" t="n">
-        <v>21.1</v>
-      </c>
       <c r="AB26" t="n">
-        <v>98.90000000000001</v>
+        <v>98</v>
       </c>
       <c r="AC26" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="AD26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE26" t="n">
         <v>8</v>
       </c>
       <c r="AF26" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AG26" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AH26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI26" t="n">
         <v>18</v>
@@ -5128,7 +5195,7 @@
         <v>19</v>
       </c>
       <c r="AK26" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AL26" t="n">
         <v>6</v>
@@ -5140,13 +5207,13 @@
         <v>5</v>
       </c>
       <c r="AO26" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AP26" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AQ26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR26" t="n">
         <v>1</v>
@@ -5164,25 +5231,25 @@
         <v>3</v>
       </c>
       <c r="AW26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ26" t="n">
         <v>13</v>
       </c>
       <c r="BA26" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BB26" t="n">
         <v>14</v>
       </c>
       <c r="BC26" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-12-2008-09</t>
+          <t>2009-01-12</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-8.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AE27" t="n">
         <v>27</v>
@@ -5301,7 +5368,7 @@
         <v>27</v>
       </c>
       <c r="AH27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AI27" t="n">
         <v>19</v>
@@ -5325,7 +5392,7 @@
         <v>13</v>
       </c>
       <c r="AP27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ27" t="n">
         <v>8</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-12-2008-09</t>
+          <t>2009-01-12</t>
         </is>
       </c>
     </row>
@@ -5471,13 +5538,13 @@
         <v>3.6</v>
       </c>
       <c r="AD28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE28" t="n">
         <v>6</v>
       </c>
       <c r="AF28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG28" t="n">
         <v>5</v>
@@ -5486,7 +5553,7 @@
         <v>1</v>
       </c>
       <c r="AI28" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ28" t="n">
         <v>17</v>
@@ -5510,7 +5577,7 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR28" t="n">
         <v>30</v>
@@ -5522,7 +5589,7 @@
         <v>24</v>
       </c>
       <c r="AU28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV28" t="n">
         <v>1</v>
@@ -5543,7 +5610,7 @@
         <v>30</v>
       </c>
       <c r="BB28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC28" t="n">
         <v>8</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-12-2008-09</t>
+          <t>2009-01-12</t>
         </is>
       </c>
     </row>
@@ -5575,61 +5642,61 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E29" t="n">
         <v>16</v>
       </c>
       <c r="F29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G29" t="n">
-        <v>0.41</v>
+        <v>0.421</v>
       </c>
       <c r="H29" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I29" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="J29" t="n">
-        <v>78.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L29" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="M29" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="N29" t="n">
         <v>0.382</v>
       </c>
       <c r="O29" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="P29" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.827</v>
+        <v>0.826</v>
       </c>
       <c r="R29" t="n">
         <v>8.9</v>
       </c>
       <c r="S29" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="T29" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="U29" t="n">
         <v>21.9</v>
       </c>
       <c r="V29" t="n">
-        <v>13.4</v>
+        <v>13.5</v>
       </c>
       <c r="W29" t="n">
         <v>6.4</v>
@@ -5641,49 +5708,49 @@
         <v>4.7</v>
       </c>
       <c r="Z29" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="AA29" t="n">
         <v>20.7</v>
       </c>
       <c r="AB29" t="n">
-        <v>97.3</v>
+        <v>97</v>
       </c>
       <c r="AC29" t="n">
-        <v>-2.3</v>
+        <v>-2.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE29" t="n">
         <v>19</v>
       </c>
       <c r="AF29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AG29" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH29" t="n">
         <v>19</v>
       </c>
-      <c r="AH29" t="n">
-        <v>15</v>
-      </c>
       <c r="AI29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ29" t="n">
         <v>22</v>
       </c>
       <c r="AK29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL29" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AM29" t="n">
         <v>19</v>
       </c>
       <c r="AN29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO29" t="n">
         <v>12</v>
@@ -5704,16 +5771,16 @@
         <v>27</v>
       </c>
       <c r="AU29" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AV29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AX29" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AY29" t="n">
         <v>12</v>
@@ -5722,10 +5789,10 @@
         <v>4</v>
       </c>
       <c r="BA29" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB29" t="n">
         <v>19</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>18</v>
       </c>
       <c r="BC29" t="n">
         <v>19</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-12-2008-09</t>
+          <t>2009-01-12</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F30" t="n">
         <v>15</v>
       </c>
       <c r="G30" t="n">
-        <v>0.605</v>
+        <v>0.595</v>
       </c>
       <c r="H30" t="n">
         <v>48.5</v>
@@ -5775,67 +5842,67 @@
         <v>38</v>
       </c>
       <c r="J30" t="n">
-        <v>79.90000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="K30" t="n">
         <v>0.476</v>
       </c>
       <c r="L30" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="M30" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="N30" t="n">
-        <v>0.34</v>
+        <v>0.336</v>
       </c>
       <c r="O30" t="n">
-        <v>21.4</v>
+        <v>21.1</v>
       </c>
       <c r="P30" t="n">
-        <v>27.7</v>
+        <v>27.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.772</v>
+        <v>0.767</v>
       </c>
       <c r="R30" t="n">
         <v>12.2</v>
       </c>
       <c r="S30" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="T30" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="U30" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="V30" t="n">
-        <v>15.5</v>
+        <v>15.7</v>
       </c>
       <c r="W30" t="n">
         <v>8.9</v>
       </c>
       <c r="X30" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y30" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AA30" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>101.9</v>
+        <v>101.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AE30" t="n">
         <v>8</v>
@@ -5847,7 +5914,7 @@
         <v>13</v>
       </c>
       <c r="AH30" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AI30" t="n">
         <v>5</v>
@@ -5868,28 +5935,28 @@
         <v>24</v>
       </c>
       <c r="AO30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AP30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT30" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU30" t="n">
         <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AW30" t="n">
         <v>1</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-12-2008-09</t>
+          <t>2009-01-12</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E31" t="n">
         <v>7</v>
       </c>
       <c r="F31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G31" t="n">
-        <v>0.189</v>
+        <v>0.194</v>
       </c>
       <c r="H31" t="n">
         <v>48.1</v>
@@ -5966,43 +6033,43 @@
         <v>4.9</v>
       </c>
       <c r="M31" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="N31" t="n">
-        <v>0.307</v>
+        <v>0.304</v>
       </c>
       <c r="O31" t="n">
-        <v>16.5</v>
+        <v>16.6</v>
       </c>
       <c r="P31" t="n">
-        <v>22.1</v>
+        <v>22.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.747</v>
+        <v>0.744</v>
       </c>
       <c r="R31" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="S31" t="n">
-        <v>28.1</v>
+        <v>28.2</v>
       </c>
       <c r="T31" t="n">
         <v>39.8</v>
       </c>
       <c r="U31" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="V31" t="n">
         <v>13.5</v>
       </c>
       <c r="W31" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="X31" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Y31" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Z31" t="n">
         <v>20.5</v>
@@ -6011,34 +6078,34 @@
         <v>19</v>
       </c>
       <c r="AB31" t="n">
-        <v>93.3</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="AC31" t="n">
         <v>-6.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
       </c>
       <c r="AF31" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AG31" t="n">
         <v>29</v>
       </c>
       <c r="AH31" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI31" t="n">
         <v>21</v>
       </c>
       <c r="AJ31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL31" t="n">
         <v>25</v>
@@ -6059,7 +6126,7 @@
         <v>26</v>
       </c>
       <c r="AR31" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AS31" t="n">
         <v>28</v>
@@ -6071,19 +6138,19 @@
         <v>17</v>
       </c>
       <c r="AV31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW31" t="n">
         <v>9</v>
       </c>
       <c r="AX31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA31" t="n">
         <v>28</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-12-2008-09</t>
+          <t>2009-01-12</t>
         </is>
       </c>
     </row>
